--- a/word_game.xlsx
+++ b/word_game.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7523873323ac77cf/방핑/WORD_GAME/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D044198156C5CEF62EFBB355D3FACC72503DEC3C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60F1672C-EC96-4254-99C3-FCFD7F51E0E3}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{6867CC2E-8E1C-4B12-B6DC-865C9B41E9F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B06BA9F-9371-4D58-8F60-44304DBBBF13}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14175" yWindow="1260" windowWidth="16200" windowHeight="15165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문제목록" sheetId="1" r:id="rId1"/>
     <sheet name="사용방법" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>정답</t>
   </si>
@@ -49,92 +50,760 @@
     <t>힌트3</t>
   </si>
   <si>
-    <t>힌트4</t>
-  </si>
-  <si>
-    <t>힌트5</t>
-  </si>
-  <si>
-    <t>자물쇠</t>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>참가자가 맞힐 실제 정답</t>
+  </si>
+  <si>
+    <t>분류코드: 자모</t>
+  </si>
+  <si>
+    <t>자물쇠 → ㅈ / ㅏ / ㅁ / ㅜ / ㄹ / ㅅ / ㅚ</t>
+  </si>
+  <si>
+    <t>분류코드: 단어</t>
+  </si>
+  <si>
+    <t>자물쇠 → 자 / 물 / 쇠</t>
+  </si>
+  <si>
+    <t>힌트1~힌트5</t>
+  </si>
+  <si>
+    <t>참가자가 힌트 버튼을 누를 때 순서대로 개인 공개</t>
+  </si>
+  <si>
+    <t>빈 힌트</t>
+  </si>
+  <si>
+    <t>뒤쪽 힌트가 필요 없으면 빈칸으로 두기</t>
+  </si>
+  <si>
+    <t>CSV 저장</t>
+  </si>
+  <si>
+    <t>엑셀에서 CSV UTF-8로 저장한 뒤 운영자 화면에서 업로드</t>
+  </si>
+  <si>
+    <t>주의</t>
+  </si>
+  <si>
+    <t>열 이름(정답, 분류코드, 힌트1~힌트5)은 그대로 유지</t>
+  </si>
+  <si>
+    <t>방핑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>자모</t>
-  </si>
-  <si>
-    <t>방탈출에서 자주 만나는 물건</t>
-  </si>
-  <si>
-    <t>열고 닫는 것과 관련 있어요</t>
-  </si>
-  <si>
-    <t>열쇠와 관련 있어요</t>
-  </si>
-  <si>
-    <t>비밀의 화원</t>
-  </si>
-  <si>
-    <t>단어</t>
-  </si>
-  <si>
-    <t>방탈출 테마 제목 예시</t>
-  </si>
-  <si>
-    <t>네 글자 제목이에요</t>
-  </si>
-  <si>
-    <t>화원이 들어가요</t>
-  </si>
-  <si>
-    <t>항목</t>
-  </si>
-  <si>
-    <t>설명</t>
-  </si>
-  <si>
-    <t>참가자가 맞힐 실제 정답</t>
-  </si>
-  <si>
-    <t>분류코드: 자모</t>
-  </si>
-  <si>
-    <t>자물쇠 → ㅈ / ㅏ / ㅁ / ㅜ / ㄹ / ㅅ / ㅚ</t>
-  </si>
-  <si>
-    <t>분류코드: 단어</t>
-  </si>
-  <si>
-    <t>자물쇠 → 자 / 물 / 쇠</t>
-  </si>
-  <si>
-    <t>힌트1~힌트5</t>
-  </si>
-  <si>
-    <t>참가자가 힌트 버튼을 누를 때 순서대로 개인 공개</t>
-  </si>
-  <si>
-    <t>빈 힌트</t>
-  </si>
-  <si>
-    <t>뒤쪽 힌트가 필요 없으면 빈칸으로 두기</t>
-  </si>
-  <si>
-    <t>CSV 저장</t>
-  </si>
-  <si>
-    <t>엑셀에서 CSV UTF-8로 저장한 뒤 운영자 화면에서 업로드</t>
-  </si>
-  <si>
-    <t>주의</t>
-  </si>
-  <si>
-    <t>열 이름(정답, 분류코드, 힌트1~힌트5)은 그대로 유지</t>
-  </si>
-  <si>
-    <t>숫자와 영어 그리고 한글</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>이걸 풀어야 나간다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>감테</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 장르 불호하는 사람이 많음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>'감성테마'줄임말</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>공테</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 장르 선호하는 사람이 많음</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>'공포테마'줄임말</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>꽃길</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>노쇼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>연방</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>혼방</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>흙길</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>야방</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>꾸금</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>연출</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>분리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>창공</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌따</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>힌트폰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>방린이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>노힌트</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>입졸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>자모</t>
+  </si>
+  <si>
+    <t>장르</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>용어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>행동</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사랑해</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>잘뽑힌 테마</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강퇴사유</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빌런</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>없는것도 만들어내는 혼자만의 싸움</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>'창조공포'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄임말</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흙길'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반대말</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>'꽃길'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>반대말</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>야외방탈출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">' </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>줄임말</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>'19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테마'를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이르는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>말</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>하루에 몇 개 가능?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>방탈러의 체력</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>테스트</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>애들은 가라!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>'방'탈출 이라고 불러도 되나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>피할 수 없으면 즐겨라, 다 돈이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>직원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">OO, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>배우</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">OO, OO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>빡세게 말아줌</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 매니저</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>너도 돈내라</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아프고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>낡고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>퀄리티 무슨 일..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>손끝에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>느껴지는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쾌감</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>우리 모두 이런 시절이 있었지..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>개천재</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>힌트따위</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>안씁니다</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>도장깨기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>매장 '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입학</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동시에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>졸업</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>..</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>'혼자하는 방탈출'의 줄임말</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>각개전투</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1, 2:1, 2:2 …</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구 없어 ?</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자물쇠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> '</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>돌려따기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> 줄임말</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>기준이 어디까지에요 ?</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -142,7 +811,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -160,6 +829,29 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -190,7 +882,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -199,6 +891,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -414,15 +1121,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="7" width="34" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15">
+    <row r="1" spans="1:5" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,1832 +1146,1570 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7">
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7">
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7">
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7">
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7">
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7">
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7">
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7">
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7">
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7">
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7">
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7">
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7">
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7">
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7">
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-    </row>
-    <row r="41" spans="1:7">
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-    </row>
-    <row r="42" spans="1:7">
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-    </row>
-    <row r="43" spans="1:7">
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-    </row>
-    <row r="44" spans="1:7">
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-    </row>
-    <row r="45" spans="1:7">
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-    </row>
-    <row r="46" spans="1:7">
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-    </row>
-    <row r="47" spans="1:7">
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-    </row>
-    <row r="48" spans="1:7">
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-    </row>
-    <row r="49" spans="1:7">
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="1:7">
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="1:7">
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" spans="1:7">
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-    </row>
-    <row r="53" spans="1:7">
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-    </row>
-    <row r="54" spans="1:7">
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-    </row>
-    <row r="55" spans="1:7">
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-    </row>
-    <row r="56" spans="1:7">
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-    </row>
-    <row r="57" spans="1:7">
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-    </row>
-    <row r="58" spans="1:7">
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-    </row>
-    <row r="59" spans="1:7">
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="1:7">
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-    </row>
-    <row r="61" spans="1:7">
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-    </row>
-    <row r="62" spans="1:7">
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-    </row>
-    <row r="63" spans="1:7">
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-    </row>
-    <row r="64" spans="1:7">
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-    </row>
-    <row r="65" spans="1:7">
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-    </row>
-    <row r="66" spans="1:7">
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-    </row>
-    <row r="67" spans="1:7">
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-      <c r="G67" s="2"/>
-    </row>
-    <row r="68" spans="1:7">
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
-    </row>
-    <row r="69" spans="1:7">
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="1:7">
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="2"/>
-      <c r="G70" s="2"/>
-    </row>
-    <row r="71" spans="1:7">
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
-    </row>
-    <row r="72" spans="1:7">
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
-      <c r="G72" s="2"/>
-    </row>
-    <row r="73" spans="1:7">
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
-      <c r="G73" s="2"/>
-    </row>
-    <row r="74" spans="1:7">
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
-      <c r="G74" s="2"/>
-    </row>
-    <row r="75" spans="1:7">
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
-      <c r="G75" s="2"/>
-    </row>
-    <row r="76" spans="1:7">
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-    </row>
-    <row r="77" spans="1:7">
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-    </row>
-    <row r="78" spans="1:7">
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:7">
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="1:7">
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="1:7">
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="1:7">
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="1:7">
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="1:7">
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="1:7">
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="1:7">
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="1:7">
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="1:7">
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="1:7">
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="1:7">
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="1:7">
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="1:7">
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="1:7">
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="1:7">
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="1:7">
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="1:7">
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="1:7">
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="1:7">
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="1:7">
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="1:7">
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="1:7">
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="1:7">
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="1:7">
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="1:7">
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="1:7">
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="1:7">
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="1:7">
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="1:7">
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="1:7">
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="1:7">
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="1:7">
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="1:7">
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="1:7">
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="1:7">
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="1:7">
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="1:7">
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="1:7">
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="1:7">
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="1:7">
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="1:7">
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="1:7">
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="1:7">
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="1:7">
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="1:7">
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="1:7">
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="1:7">
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="1:7">
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="1:7">
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="1:7">
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="1:7">
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="1:7">
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="1:7">
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="1:7">
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="1:7">
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="1:7">
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="1:7">
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="1:7">
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="1:7">
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row r="139" spans="1:7">
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row r="140" spans="1:7">
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row r="141" spans="1:7">
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row r="142" spans="1:7">
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row r="143" spans="1:7">
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row r="144" spans="1:7">
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row r="145" spans="1:7">
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7">
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row r="147" spans="1:7">
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-    </row>
-    <row r="148" spans="1:7">
+    </row>
+    <row r="148" spans="1:5">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="1:7">
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-    </row>
-    <row r="150" spans="1:7">
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-    </row>
-    <row r="151" spans="1:7">
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row r="152" spans="1:7">
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-    </row>
-    <row r="153" spans="1:7">
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row r="154" spans="1:7">
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-    </row>
-    <row r="155" spans="1:7">
+    </row>
+    <row r="155" spans="1:5">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-    </row>
-    <row r="156" spans="1:7">
+    </row>
+    <row r="156" spans="1:5">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-    </row>
-    <row r="157" spans="1:7">
+    </row>
+    <row r="157" spans="1:5">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="1:7">
+    </row>
+    <row r="158" spans="1:5">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-    </row>
-    <row r="159" spans="1:7">
+    </row>
+    <row r="159" spans="1:5">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row r="160" spans="1:7">
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-    </row>
-    <row r="161" spans="1:7">
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-    </row>
-    <row r="162" spans="1:7">
+    </row>
+    <row r="162" spans="1:5">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-    </row>
-    <row r="163" spans="1:7">
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-    </row>
-    <row r="164" spans="1:7">
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-    </row>
-    <row r="165" spans="1:7">
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
-      <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-    </row>
-    <row r="166" spans="1:7">
+    </row>
+    <row r="166" spans="1:5">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
-      <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-    </row>
-    <row r="167" spans="1:7">
+    </row>
+    <row r="167" spans="1:5">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-    </row>
-    <row r="168" spans="1:7">
+    </row>
+    <row r="168" spans="1:5">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-    </row>
-    <row r="169" spans="1:7">
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-    </row>
-    <row r="170" spans="1:7">
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
-      <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-    </row>
-    <row r="171" spans="1:7">
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
-      <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-    </row>
-    <row r="172" spans="1:7">
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-    </row>
-    <row r="173" spans="1:7">
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-    </row>
-    <row r="174" spans="1:7">
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-    </row>
-    <row r="175" spans="1:7">
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
-    </row>
-    <row r="176" spans="1:7">
+    </row>
+    <row r="176" spans="1:5">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-    </row>
-    <row r="177" spans="1:7">
+    </row>
+    <row r="177" spans="1:5">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
-      <c r="F177" s="2"/>
-      <c r="G177" s="2"/>
-    </row>
-    <row r="178" spans="1:7">
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-    </row>
-    <row r="179" spans="1:7">
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
-      <c r="F179" s="2"/>
-      <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="1:7">
+    </row>
+    <row r="180" spans="1:5">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
-      <c r="F180" s="2"/>
-      <c r="G180" s="2"/>
-    </row>
-    <row r="181" spans="1:7">
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
-      <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-    </row>
-    <row r="182" spans="1:7">
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-    </row>
-    <row r="183" spans="1:7">
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
-      <c r="F183" s="2"/>
-      <c r="G183" s="2"/>
-    </row>
-    <row r="184" spans="1:7">
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
-      <c r="F184" s="2"/>
-      <c r="G184" s="2"/>
-    </row>
-    <row r="185" spans="1:7">
+    </row>
+    <row r="185" spans="1:5">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
-      <c r="F185" s="2"/>
-      <c r="G185" s="2"/>
-    </row>
-    <row r="186" spans="1:7">
+    </row>
+    <row r="186" spans="1:5">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
-      <c r="G186" s="2"/>
-    </row>
-    <row r="187" spans="1:7">
+    </row>
+    <row r="187" spans="1:5">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
-      <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-    </row>
-    <row r="188" spans="1:7">
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
-      <c r="F188" s="2"/>
-      <c r="G188" s="2"/>
-    </row>
-    <row r="189" spans="1:7">
+    </row>
+    <row r="189" spans="1:5">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
-      <c r="F189" s="2"/>
-      <c r="G189" s="2"/>
-    </row>
-    <row r="190" spans="1:7">
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
-      <c r="F190" s="2"/>
-      <c r="G190" s="2"/>
-    </row>
-    <row r="191" spans="1:7">
+    </row>
+    <row r="191" spans="1:5">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
-      <c r="F191" s="2"/>
-      <c r="G191" s="2"/>
-    </row>
-    <row r="192" spans="1:7">
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
-      <c r="F192" s="2"/>
-      <c r="G192" s="2"/>
-    </row>
-    <row r="193" spans="1:7">
+    </row>
+    <row r="193" spans="1:5">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
-      <c r="G193" s="2"/>
-    </row>
-    <row r="194" spans="1:7">
+    </row>
+    <row r="194" spans="1:5">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
-      <c r="F194" s="2"/>
-      <c r="G194" s="2"/>
-    </row>
-    <row r="195" spans="1:7">
+    </row>
+    <row r="195" spans="1:5">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
-      <c r="F195" s="2"/>
-      <c r="G195" s="2"/>
-    </row>
-    <row r="196" spans="1:7">
+    </row>
+    <row r="196" spans="1:5">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
-      <c r="F196" s="2"/>
-      <c r="G196" s="2"/>
-    </row>
-    <row r="197" spans="1:7">
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
-      <c r="F197" s="2"/>
-      <c r="G197" s="2"/>
-    </row>
-    <row r="198" spans="1:7">
+    </row>
+    <row r="198" spans="1:5">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
-      <c r="F198" s="2"/>
-      <c r="G198" s="2"/>
-    </row>
-    <row r="199" spans="1:7">
-      <c r="A199" s="2"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-      <c r="E199" s="2"/>
-      <c r="F199" s="2"/>
-      <c r="G199" s="2"/>
-    </row>
-    <row r="200" spans="1:7">
-      <c r="A200" s="2"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="E200" s="2"/>
-      <c r="F200" s="2"/>
-      <c r="G200" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B500" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B2:B498" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"자모,단어"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2282,10 +2728,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="3" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2293,55 +2739,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2395,5 +2841,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>